--- a/artfynd/A 59319-2023 artfynd.xlsx
+++ b/artfynd/A 59319-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59319-2023 artfynd.xlsx
+++ b/artfynd/A 59319-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113406698</v>
+        <v>113406713</v>
       </c>
       <c r="B2" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573412</v>
+        <v>573407</v>
       </c>
       <c r="R2" t="n">
-        <v>6408701</v>
+        <v>6408717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På marken ngn meter från tallen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,51 +789,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113406657</v>
+        <v>113406745</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573376</v>
+        <v>573415</v>
       </c>
       <c r="R3" t="n">
-        <v>6408735</v>
+        <v>6408692</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,6 +871,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På foten på en gammal tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,51 +903,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113406613</v>
+        <v>113413926</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573369</v>
+        <v>573391</v>
       </c>
       <c r="R4" t="n">
-        <v>6408721</v>
+        <v>6408668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,12 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113406648</v>
+        <v>113406562</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,11 +1040,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1072,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573375</v>
+        <v>573393</v>
       </c>
       <c r="R5" t="n">
-        <v>6408731</v>
+        <v>6408707</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,15 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113406691</v>
+        <v>113406580</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,7 +1148,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1187,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573410</v>
+        <v>573395</v>
       </c>
       <c r="R6" t="n">
-        <v>6408701</v>
+        <v>6408713</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,12 +1231,7 @@
         <v>113406594</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,15 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113406580</v>
+        <v>113406605</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1368,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1417,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573395</v>
+        <v>573388</v>
       </c>
       <c r="R8" t="n">
-        <v>6408713</v>
+        <v>6408716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,15 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113406562</v>
+        <v>113406613</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,7 +1476,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1528,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573393</v>
+        <v>573369</v>
       </c>
       <c r="R9" t="n">
-        <v>6408707</v>
+        <v>6408721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,42 +1558,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113406685</v>
+        <v>113406630</v>
       </c>
       <c r="B10" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1643,10 +1605,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573355</v>
+        <v>573371</v>
       </c>
       <c r="R10" t="n">
-        <v>6408737</v>
+        <v>6408718</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,50 +1668,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113406745</v>
+        <v>113406648</v>
       </c>
       <c r="B11" t="n">
-        <v>90330</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1110</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1757,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573415</v>
+        <v>573375</v>
       </c>
       <c r="R11" t="n">
-        <v>6408692</v>
+        <v>6408731</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,11 +1751,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På foten på en gammal tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,15 +1778,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113406676</v>
+        <v>113406657</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1806,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1873,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573366</v>
+        <v>573376</v>
       </c>
       <c r="R12" t="n">
-        <v>6408743</v>
+        <v>6408735</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,15 +1888,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113406697</v>
+        <v>113406672</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,12 +1916,12 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1984,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>573412</v>
+        <v>573366</v>
       </c>
       <c r="R13" t="n">
-        <v>6408701</v>
+        <v>6408721</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,15 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113406672</v>
+        <v>113406676</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,12 +2022,12 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2098,7 +2040,7 @@
         <v>573366</v>
       </c>
       <c r="R14" t="n">
-        <v>6408721</v>
+        <v>6408743</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2158,15 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113406630</v>
+        <v>113406691</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2130,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2210,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573371</v>
+        <v>573410</v>
       </c>
       <c r="R15" t="n">
-        <v>6408718</v>
+        <v>6408701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2273,50 +2210,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113406713</v>
+        <v>113406697</v>
       </c>
       <c r="B16" t="n">
-        <v>90330</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1110</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2324,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>573407</v>
+        <v>573412</v>
       </c>
       <c r="R16" t="n">
-        <v>6408717</v>
+        <v>6408701</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,11 +2289,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På marken ngn meter från tallen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,15 +2316,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113406605</v>
+        <v>113413993</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2427,7 +2346,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2444,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>573388</v>
+        <v>573365</v>
       </c>
       <c r="R17" t="n">
-        <v>6408716</v>
+        <v>6408750</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,12 +2393,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,42 +2426,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113414055</v>
+        <v>113414072</v>
       </c>
       <c r="B18" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2562,7 +2476,7 @@
         <v>573398</v>
       </c>
       <c r="R18" t="n">
-        <v>6408694</v>
+        <v>6408705</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,15 +2536,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113413926</v>
+        <v>113406685</v>
       </c>
       <c r="B19" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,34 +2547,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2673,10 +2583,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>573391</v>
+        <v>573355</v>
       </c>
       <c r="R19" t="n">
-        <v>6408668</v>
+        <v>6408737</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2703,12 +2613,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,42 +2646,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113414072</v>
+        <v>113406698</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2788,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>573398</v>
+        <v>573412</v>
       </c>
       <c r="R20" t="n">
-        <v>6408705</v>
+        <v>6408701</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2818,12 +2723,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,6 +2753,116 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113414055</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 59319, Greby, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>573398</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6408694</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
